--- a/output/roomself_excel/5607.xlsx
+++ b/output/roomself_excel/5607.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,20 +466,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>431640</v>
+        <v>91296</v>
       </c>
       <c r="D2" t="n">
-        <v>10144</v>
+        <v>2420</v>
       </c>
       <c r="E2" t="n">
-        <v>1030</v>
+        <v>336</v>
       </c>
       <c r="F2" t="n">
-        <v>664</v>
+        <v>307</v>
       </c>
     </row>
     <row r="3">
@@ -488,20 +488,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>23760</v>
+        <v>228118</v>
       </c>
       <c r="D3" t="n">
-        <v>1432</v>
+        <v>4792</v>
       </c>
       <c r="E3" t="n">
-        <v>88</v>
+        <v>724</v>
       </c>
       <c r="F3" t="n">
-        <v>19</v>
+        <v>310</v>
       </c>
     </row>
     <row r="4">
@@ -510,20 +510,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>91296</v>
+        <v>48548</v>
       </c>
       <c r="D4" t="n">
-        <v>2420</v>
+        <v>1836</v>
       </c>
       <c r="E4" t="n">
-        <v>336</v>
+        <v>306</v>
       </c>
       <c r="F4" t="n">
-        <v>307</v>
+        <v>191</v>
       </c>
     </row>
     <row r="5">
@@ -532,20 +532,20 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>18513</v>
+        <v>92156</v>
       </c>
       <c r="D5" t="n">
-        <v>1096</v>
+        <v>2476</v>
       </c>
       <c r="E5" t="n">
-        <v>121</v>
+        <v>351</v>
       </c>
       <c r="F5" t="n">
-        <v>19</v>
+        <v>306</v>
       </c>
     </row>
     <row r="6">
@@ -554,17 +554,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>13205</v>
+        <v>74496</v>
       </c>
       <c r="D6" t="n">
-        <v>936</v>
+        <v>2188</v>
       </c>
       <c r="E6" t="n">
-        <v>139</v>
+        <v>291</v>
       </c>
       <c r="F6" t="n">
         <v>19</v>
@@ -576,20 +576,20 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Garage</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>135520</v>
+        <v>62818</v>
       </c>
       <c r="D7" t="n">
-        <v>2992</v>
+        <v>2640</v>
       </c>
       <c r="E7" t="n">
-        <v>459</v>
+        <v>131</v>
       </c>
       <c r="F7" t="n">
-        <v>327</v>
+        <v>123</v>
       </c>
     </row>
     <row r="8">
@@ -598,20 +598,20 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>113444</v>
+        <v>23760</v>
       </c>
       <c r="D8" t="n">
-        <v>3396</v>
+        <v>1432</v>
       </c>
       <c r="E8" t="n">
-        <v>560</v>
+        <v>88</v>
       </c>
       <c r="F8" t="n">
-        <v>327</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9">
@@ -642,17 +642,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>74496</v>
+        <v>35346</v>
       </c>
       <c r="D10" t="n">
-        <v>2188</v>
+        <v>1580</v>
       </c>
       <c r="E10" t="n">
-        <v>291</v>
+        <v>137</v>
       </c>
       <c r="F10" t="n">
         <v>19</v>
@@ -664,14 +664,14 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>22605</v>
+        <v>6279</v>
       </c>
       <c r="D11" t="n">
-        <v>1208</v>
+        <v>640</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -686,17 +686,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>47628</v>
+        <v>34830</v>
       </c>
       <c r="D12" t="n">
-        <v>2864</v>
+        <v>1572</v>
       </c>
       <c r="E12" t="n">
-        <v>296</v>
+        <v>135</v>
       </c>
       <c r="F12" t="n">
         <v>19</v>
@@ -708,20 +708,20 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Garage</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>35346</v>
+        <v>135520</v>
       </c>
       <c r="D13" t="n">
-        <v>1580</v>
+        <v>2992</v>
       </c>
       <c r="E13" t="n">
-        <v>137</v>
+        <v>459</v>
       </c>
       <c r="F13" t="n">
-        <v>19</v>
+        <v>327</v>
       </c>
     </row>
     <row r="14">
@@ -730,20 +730,20 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>6279</v>
+        <v>18513</v>
       </c>
       <c r="D14" t="n">
-        <v>640</v>
+        <v>1096</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>121</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
     </row>
     <row r="15">
@@ -756,16 +756,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>37125</v>
+        <v>13205</v>
       </c>
       <c r="D15" t="n">
-        <v>1640</v>
+        <v>936</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>139</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
     </row>
     <row r="16">
@@ -774,20 +774,86 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>34830</v>
+        <v>113444</v>
       </c>
       <c r="D16" t="n">
-        <v>1572</v>
+        <v>3396</v>
       </c>
       <c r="E16" t="n">
-        <v>135</v>
+        <v>560</v>
       </c>
       <c r="F16" t="n">
-        <v>19</v>
+        <v>327</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>22605</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1208</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>47628</v>
+      </c>
+      <c r="D18" t="n">
+        <v>2864</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>37125</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1640</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/output/roomself_excel/5607.xlsx
+++ b/output/roomself_excel/5607.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,32 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallLength</t>
+          <t>WallDir_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallWidth</t>
+          <t>ExtWallLength_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_2</t>
         </is>
       </c>
     </row>
@@ -475,11 +495,27 @@
       <c r="D2" t="n">
         <v>2420</v>
       </c>
-      <c r="E2" t="n">
-        <v>336</v>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F2" t="n">
-        <v>307</v>
+        <v>317</v>
+      </c>
+      <c r="G2" t="n">
+        <v>19</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>288</v>
+      </c>
+      <c r="J2" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="3">
@@ -497,11 +533,27 @@
       <c r="D3" t="n">
         <v>4792</v>
       </c>
-      <c r="E3" t="n">
-        <v>724</v>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F3" t="n">
-        <v>310</v>
+        <v>686</v>
+      </c>
+      <c r="G3" t="n">
+        <v>19</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>291</v>
+      </c>
+      <c r="J3" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="4">
@@ -519,11 +571,27 @@
       <c r="D4" t="n">
         <v>1836</v>
       </c>
-      <c r="E4" t="n">
-        <v>306</v>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F4" t="n">
-        <v>191</v>
+        <v>287</v>
+      </c>
+      <c r="G4" t="n">
+        <v>19</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>172</v>
+      </c>
+      <c r="J4" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="5">
@@ -541,11 +609,27 @@
       <c r="D5" t="n">
         <v>2476</v>
       </c>
-      <c r="E5" t="n">
-        <v>351</v>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F5" t="n">
-        <v>306</v>
+        <v>332</v>
+      </c>
+      <c r="G5" t="n">
+        <v>19</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>270</v>
+      </c>
+      <c r="J5" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="6">
@@ -563,11 +647,27 @@
       <c r="D6" t="n">
         <v>2188</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
         <v>291</v>
       </c>
-      <c r="F6" t="n">
-        <v>19</v>
+      <c r="G6" t="n">
+        <v>19</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>256</v>
+      </c>
+      <c r="J6" t="n">
+        <v>18</v>
       </c>
     </row>
     <row r="7">
@@ -585,12 +685,20 @@
       <c r="D7" t="n">
         <v>2640</v>
       </c>
-      <c r="E7" t="n">
-        <v>131</v>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F7" t="n">
-        <v>123</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="G7" t="n">
+        <v>19</v>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -607,12 +715,20 @@
       <c r="D8" t="n">
         <v>1432</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
         <v>88</v>
       </c>
-      <c r="F8" t="n">
-        <v>19</v>
-      </c>
+      <c r="G8" t="n">
+        <v>19</v>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -629,11 +745,27 @@
       <c r="D9" t="n">
         <v>1724</v>
       </c>
-      <c r="E9" t="n">
-        <v>277</v>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F9" t="n">
-        <v>192</v>
+        <v>258</v>
+      </c>
+      <c r="G9" t="n">
+        <v>19</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>173</v>
+      </c>
+      <c r="J9" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="10">
@@ -651,12 +783,20 @@
       <c r="D10" t="n">
         <v>1580</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
         <v>137</v>
       </c>
-      <c r="F10" t="n">
-        <v>19</v>
-      </c>
+      <c r="G10" t="n">
+        <v>19</v>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -673,12 +813,12 @@
       <c r="D11" t="n">
         <v>640</v>
       </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -695,11 +835,27 @@
       <c r="D12" t="n">
         <v>1572</v>
       </c>
-      <c r="E12" t="n">
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
         <v>135</v>
       </c>
-      <c r="F12" t="n">
-        <v>19</v>
+      <c r="G12" t="n">
+        <v>19</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>258</v>
+      </c>
+      <c r="J12" t="n">
+        <v>18</v>
       </c>
     </row>
     <row r="13">
@@ -717,11 +873,27 @@
       <c r="D13" t="n">
         <v>2992</v>
       </c>
-      <c r="E13" t="n">
-        <v>459</v>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F13" t="n">
-        <v>327</v>
+        <v>440</v>
+      </c>
+      <c r="G13" t="n">
+        <v>19</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>308</v>
+      </c>
+      <c r="J13" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="14">
@@ -739,12 +911,20 @@
       <c r="D14" t="n">
         <v>1096</v>
       </c>
-      <c r="E14" t="n">
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
         <v>121</v>
       </c>
-      <c r="F14" t="n">
-        <v>19</v>
-      </c>
+      <c r="G14" t="n">
+        <v>19</v>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -761,12 +941,20 @@
       <c r="D15" t="n">
         <v>936</v>
       </c>
-      <c r="E15" t="n">
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
         <v>139</v>
       </c>
-      <c r="F15" t="n">
-        <v>19</v>
-      </c>
+      <c r="G15" t="n">
+        <v>19</v>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -783,11 +971,27 @@
       <c r="D16" t="n">
         <v>3396</v>
       </c>
-      <c r="E16" t="n">
-        <v>560</v>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F16" t="n">
-        <v>327</v>
+        <v>264</v>
+      </c>
+      <c r="G16" t="n">
+        <v>19</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>116</v>
+      </c>
+      <c r="J16" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="17">
@@ -805,12 +1009,12 @@
       <c r="D17" t="n">
         <v>1208</v>
       </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -827,12 +1031,20 @@
       <c r="D18" t="n">
         <v>2864</v>
       </c>
-      <c r="E18" t="n">
-        <v>0</v>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
-      </c>
+        <v>154</v>
+      </c>
+      <c r="G18" t="n">
+        <v>18</v>
+      </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -849,12 +1061,20 @@
       <c r="D19" t="n">
         <v>1640</v>
       </c>
-      <c r="E19" t="n">
-        <v>0</v>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
-      </c>
+        <v>275</v>
+      </c>
+      <c r="G19" t="n">
+        <v>18</v>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
